--- a/Assets/Project/Csv/Crops/Crops.xlsx
+++ b/Assets/Project/Csv/Crops/Crops.xlsx
@@ -5,76 +5,57 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\GitLab\Dairy Farm\Assets\Project\Csv\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ycjun\OneDrive\문서\Projects\Git\Dairy Farm\Assets\Project\Csv\Crops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AEE019D-A228-44B7-BC46-22ACA04C6785}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6056388-1564-4C78-BE95-0B26E464C354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{0F09CBD5-735E-42CB-A283-6E4DE4193512}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <t>index</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>nameTag</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>season</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>result_ItemIndex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>days_ToMaturity</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+  <si>
+    <t>{id/int/UNIQUE/NOT NULL}</t>
+  </si>
+  <si>
+    <t>{name/string/UNIQUE/NOT NULL}</t>
+  </si>
+  <si>
+    <t>{season/enum/NOT NULL}</t>
+  </si>
+  <si>
+    <t>{daysToMaturity/int/NOT NULL}</t>
+  </si>
+  <si>
+    <t>{growthSpriteIds/AssetID[]/NOT NULL}</t>
+  </si>
+  <si>
+    <t>{seedName/string/UNIQUE/NOT NULL}</t>
   </si>
   <si>
     <t>쌀</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>토마토</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>호박</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>딸기</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>옥수수</t>
+  </si>
+  <si>
+    <t>{seedId/int/UNIQUE/NOT NULL}</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -99,20 +80,41 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -121,10 +123,18 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -458,117 +468,136 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC38FBB7-EF70-4387-BA44-4B6A19040DF1}">
-  <dimension ref="A1:E6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.25" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="30.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="36.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="31.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="37.5" style="1" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="3">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="3">
+        <v>0</v>
+      </c>
+      <c r="D2" s="3">
+        <v>1</v>
+      </c>
+      <c r="E2" s="3">
+        <v>10001</v>
+      </c>
+      <c r="F2" s="3"/>
+      <c r="G2" s="4"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="3">
+        <v>101</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>10101</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="4"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="3">
+        <v>201</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="3">
+        <v>2</v>
+      </c>
+      <c r="D4" s="3">
+        <v>1</v>
+      </c>
+      <c r="E4" s="3">
+        <v>10201</v>
+      </c>
+      <c r="F4" s="3"/>
+      <c r="G4" s="4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="3">
+        <v>301</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="3">
         <v>3</v>
       </c>
+      <c r="D5" s="3">
+        <v>1</v>
+      </c>
+      <c r="E5" s="3">
+        <v>10301</v>
+      </c>
+      <c r="F5" s="3"/>
+      <c r="G5" s="4"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>10001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>10101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>201</v>
-      </c>
-      <c r="B4" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>10201</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>301</v>
-      </c>
-      <c r="B5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="3">
+        <v>401</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="3">
         <v>3</v>
       </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
         <v>10301</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>401</v>
-      </c>
-      <c r="B6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6">
-        <v>3</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>10301</v>
-      </c>
+      <c r="F6" s="3"/>
+      <c r="G6" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
